--- a/docs/database-sch.xlsx
+++ b/docs/database-sch.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\plant-care\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6251DD-86AD-49D6-8FE0-8AE83A9C6DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC371B3B-E6CC-46AC-8E76-2DB89FF55EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="432" windowWidth="23256" windowHeight="12636" activeTab="1" xr2:uid="{E5B0560F-CD2C-4C9C-AFFC-F1AB59BD879B}"/>
   </bookViews>
@@ -34,6 +34,174 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Dipanjan Deb</author>
+  </authors>
+  <commentList>
+    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{FE78B891-464D-4DC2-B8E7-555BA06C789D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Dipanjan Deb:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+for debugging faulty location</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Dipanjan Deb</author>
+  </authors>
+  <commentList>
+    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{09C10816-D9D6-4B56-BC5C-B1C96ADE514F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Dipanjan Deb:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+For Better Searching</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N2" authorId="0" shapeId="0" xr:uid="{0438BC03-B592-41EF-ACA6-558DEFDBDA9B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Dipanjan Deb:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+for UI tags
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P2" authorId="0" shapeId="0" xr:uid="{D14B4DF2-1E3A-480B-8996-620A1F81B0C2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Dipanjan Deb:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+can be rejected if not needed
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q2" authorId="0" shapeId="0" xr:uid="{E2B0A986-DC21-4B74-A4D5-378DE63DE407}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Dipanjan Deb:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Verify
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R2" authorId="0" shapeId="0" xr:uid="{C5B48FED-D883-428A-93FC-2DEE24D7E011}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Dipanjan Deb:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Verify
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="225">
   <si>
@@ -716,7 +884,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -749,8 +917,40 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -766,6 +966,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -798,7 +1004,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -809,6 +1015,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1125,7 +1337,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85E6E06E-F72F-4212-8A63-F00BF30E8810}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85E6E06E-F72F-4212-8A63-F00BF30E8810}">
   <dimension ref="A1:P5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1222,7 +1434,7 @@
       <c r="J2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="6" t="s">
         <v>29</v>
       </c>
       <c r="L2" s="2">
@@ -1272,7 +1484,7 @@
       <c r="J3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="6" t="s">
         <v>35</v>
       </c>
       <c r="L3" s="2">
@@ -1322,7 +1534,7 @@
       <c r="J4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="6" t="s">
         <v>42</v>
       </c>
       <c r="L4" s="2">
@@ -1372,7 +1584,7 @@
       <c r="J5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="6" t="s">
         <v>29</v>
       </c>
       <c r="L5" s="2">
@@ -1399,11 +1611,12 @@
     <hyperlink ref="B5" r:id="rId4" xr:uid="{D3C021F6-59D9-44EE-A138-118137E03D44}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F53B8D3-805E-46C6-8C6C-2943299F919D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F53B8D3-805E-46C6-8C6C-2943299F919D}">
   <dimension ref="A1:T31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1421,7 +1634,7 @@
     <col min="12" max="12" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="50.77734375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="48.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16" customWidth="1"/>
     <col min="16" max="16" width="38.88671875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12.77734375" bestFit="1" customWidth="1"/>
@@ -1497,7 +1710,7 @@
       <c r="C2" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="7" t="s">
         <v>72</v>
       </c>
       <c r="E2" s="5" t="s">
@@ -1527,17 +1740,17 @@
       <c r="M2" s="5">
         <v>42</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="7" t="s">
         <v>74</v>
       </c>
       <c r="O2" s="5"/>
       <c r="P2" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="Q2" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="R2" s="5" t="s">
+      <c r="Q2" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R2" s="7" t="s">
         <v>76</v>
       </c>
       <c r="S2" s="5" t="s">
@@ -3202,5 +3415,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/docs/database-sch.xlsx
+++ b/docs/database-sch.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\plant-care\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC371B3B-E6CC-46AC-8E76-2DB89FF55EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{580A6E28-171E-4177-A655-C8F00EC0EC78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="432" windowWidth="23256" windowHeight="12636" activeTab="1" xr2:uid="{E5B0560F-CD2C-4C9C-AFFC-F1AB59BD879B}"/>
+    <workbookView xWindow="-108" yWindow="432" windowWidth="23256" windowHeight="12636" xr2:uid="{E5B0560F-CD2C-4C9C-AFFC-F1AB59BD879B}"/>
   </bookViews>
   <sheets>
     <sheet name="profiles" sheetId="1" r:id="rId1"/>
@@ -203,7 +203,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="227">
   <si>
     <t>id</t>
   </si>
@@ -878,6 +878,12 @@
   </si>
   <si>
     <t>{bright-light, flowering, statement}</t>
+  </si>
+  <si>
+    <t>floor_number</t>
+  </si>
+  <si>
+    <t>0 - ground</t>
   </si>
 </sst>
 </file>
@@ -1338,7 +1344,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85E6E06E-F72F-4212-8A63-F00BF30E8810}">
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.77734375" bestFit="1" customWidth="1"/>
@@ -1350,10 +1356,11 @@
     <col min="10" max="10" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.21875" customWidth="1"/>
+    <col min="16" max="17" width="23.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1397,13 +1404,16 @@
         <v>12</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
@@ -1447,13 +1457,16 @@
         <v>30</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>31</v>
+        <v>226</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q2" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
@@ -1496,14 +1509,17 @@
       <c r="N3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" s="2">
+        <v>1</v>
+      </c>
+      <c r="P3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>18</v>
       </c>
@@ -1546,14 +1562,17 @@
       <c r="N4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O4" s="2" t="s">
-        <v>44</v>
+      <c r="O4" s="2">
+        <v>2</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q4" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
@@ -1596,10 +1615,13 @@
       <c r="N5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="O5" s="2">
+        <v>21</v>
+      </c>
+      <c r="P5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="P5" s="2" t="s">
+      <c r="Q5" s="2" t="s">
         <v>48</v>
       </c>
     </row>
